--- a/artfynd/A 23008-2022 artfynd.xlsx
+++ b/artfynd/A 23008-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23008-2022 artfynd.xlsx
+++ b/artfynd/A 23008-2022 artfynd.xlsx
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96747779</v>
+        <v>102942300</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjälamark, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754797.9782672105</v>
+        <v>754837</v>
       </c>
       <c r="R2" t="n">
-        <v>7094623.802437202</v>
+        <v>7094612</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +765,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Andreas Estensen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Andreas Estensen, Tonje Lindmark, Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96747926</v>
+        <v>96747779</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,43 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjälamark, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754844.5665227005</v>
+        <v>754798</v>
       </c>
       <c r="R3" t="n">
-        <v>7094655.476912469</v>
+        <v>7094624</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +874,9 @@
           <t>2021-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102942298</v>
+        <v>102942288</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,19 +938,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjälamark, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754824.0016644523</v>
+        <v>754884</v>
       </c>
       <c r="R4" t="n">
-        <v>7094598.053098327</v>
+        <v>7094724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,27 +982,18 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,22 +1004,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,37 +1032,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102942297</v>
+        <v>96747926</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1092,9 +1065,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1103,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754827.9982120959</v>
+        <v>754844</v>
       </c>
       <c r="R5" t="n">
-        <v>7094597.93680894</v>
+        <v>7094655</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1106,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,58 +1122,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Estensen</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Tonje Lindmark, Carl Jansson</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102942300</v>
+        <v>102942297</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1220,7 +1173,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1229,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754837.00806743</v>
+        <v>754828</v>
       </c>
       <c r="R6" t="n">
-        <v>7094612.387345598</v>
+        <v>7094598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,21 +1215,11 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1289,26 +1232,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,12 +1252,7 @@
         <v>102942299</v>
       </c>
       <c r="B7" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,6 +1262,11 @@
       <c r="E7" t="n">
         <v>6040186</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Leptoporus mollis</t>
@@ -1370,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754818.1730855091</v>
+        <v>754818</v>
       </c>
       <c r="R7" t="n">
-        <v>7094598.904750221</v>
+        <v>7094599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,19 +1326,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 23008-2022 artfynd.xlsx
+++ b/artfynd/A 23008-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102942300</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96747779</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102942288</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96747926</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102942297</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,8 +1408,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102942299</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>